--- a/artfynd/A 16884-2025 artfynd.xlsx
+++ b/artfynd/A 16884-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74665480</v>
       </c>
       <c r="B2" t="n">
-        <v>104505</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107006</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551516.8280227121</v>
+        <v>551517</v>
       </c>
       <c r="R2" t="n">
-        <v>6363959.161078499</v>
+        <v>6363959</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1987-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1987-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 16884-2025 artfynd.xlsx
+++ b/artfynd/A 16884-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74665480</v>
       </c>
       <c r="B2" t="n">
-        <v>107006</v>
+        <v>107015</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16884-2025 artfynd.xlsx
+++ b/artfynd/A 16884-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74665480</v>
       </c>
       <c r="B2" t="n">
-        <v>107015</v>
+        <v>107020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16884-2025 artfynd.xlsx
+++ b/artfynd/A 16884-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74665480</v>
       </c>
       <c r="B2" t="n">
-        <v>107020</v>
+        <v>107048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16884-2025 artfynd.xlsx
+++ b/artfynd/A 16884-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74665480</v>
       </c>
       <c r="B2" t="n">
-        <v>107048</v>
+        <v>107054</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16884-2025 artfynd.xlsx
+++ b/artfynd/A 16884-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74665480</v>
       </c>
       <c r="B2" t="n">
-        <v>107054</v>
+        <v>107061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16884-2025 artfynd.xlsx
+++ b/artfynd/A 16884-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74665480</v>
       </c>
       <c r="B2" t="n">
-        <v>107061</v>
+        <v>107065</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16884-2025 artfynd.xlsx
+++ b/artfynd/A 16884-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74665480</v>
       </c>
       <c r="B2" t="n">
-        <v>107065</v>
+        <v>107073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16884-2025 artfynd.xlsx
+++ b/artfynd/A 16884-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74665480</v>
       </c>
       <c r="B2" t="n">
-        <v>107076</v>
+        <v>107081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16884-2025 artfynd.xlsx
+++ b/artfynd/A 16884-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74665480</v>
       </c>
       <c r="B2" t="n">
-        <v>107081</v>
+        <v>107089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16884-2025 artfynd.xlsx
+++ b/artfynd/A 16884-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74665480</v>
       </c>
       <c r="B2" t="n">
-        <v>107089</v>
+        <v>107099</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16884-2025 artfynd.xlsx
+++ b/artfynd/A 16884-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74665480</v>
+        <v>42393</v>
       </c>
       <c r="B2" t="n">
-        <v>107099</v>
+        <v>56895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221735</v>
+        <v>100088</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Åkerrödtoppa</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odontites vernus</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bellardi) Dumort.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hagelsrum, Sm</t>
+          <t>Kräftdammarna, Hagelsrum, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551517</v>
+        <v>551648</v>
       </c>
       <c r="R2" t="n">
-        <v>6363959</v>
+        <v>6363831</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +749,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1987-01-01</t>
+          <t>2008-07-02</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1987-12-31</t>
+          <t>2008-07-02</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6G3a 0531. SOM: Odontites vernus. LEG: Linus Svensson</t>
+          <t>Slingrade sig över vägen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,15 +784,117 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Calle Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Calle Ljungberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>74665480</v>
+      </c>
+      <c r="B3" t="n">
+        <v>107623</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221735</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Åkerrödtoppa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Odontites vernus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Bellardi) Dumort.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hagelsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>551517</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6363959</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Målilla</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1987-01-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1987-12-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6G3a 0531. SOM: Odontites vernus. LEG: Linus Svensson</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Via Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>

--- a/artfynd/A 16884-2025 artfynd.xlsx
+++ b/artfynd/A 16884-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/42393</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,8 +909,17 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74665480</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>